--- a/artfynd/A 21962-2025 artfynd.xlsx
+++ b/artfynd/A 21962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,250 +793,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>118325347</v>
-      </c>
-      <c r="B3" t="n">
-        <v>97853</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Fäbodmyran (Fäbodmyran), Ång</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>637778</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7013567</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Boteå</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>118511432</v>
-      </c>
-      <c r="B4" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Följansbodarna, SO om, Ång</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>637784</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7013567</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Boteå</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson, Kamilla Andersson, Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SBF Florainventering i Ångermanland 2024</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21962-2025 artfynd.xlsx
+++ b/artfynd/A 21962-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>62198626</v>
       </c>
       <c r="B2" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638280.2745429629</v>
+        <v>638280</v>
       </c>
       <c r="R2" t="n">
-        <v>7012660.756674793</v>
+        <v>7012661</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,19 +752,9 @@
           <t>2016-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-06-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 21962-2025 artfynd.xlsx
+++ b/artfynd/A 21962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,8 +783,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62198626</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>